--- a/public/data/三国历史短剧1000集策划总表.xlsx
+++ b/public/data/三国历史短剧1000集策划总表.xlsx
@@ -22258,7 +22258,7 @@
         <x:v>《三国志》</x:v>
       </x:c>
       <x:c r="F638" s="110" t="str">
-        <x:v>卷九、卷十七、卷十八相关将领传</x:v>
+        <x:v>卷三十六《关张马黄赵传》及裴松之注；卷九、卷十七、卷十八相关将领传</x:v>
       </x:c>
       <x:c r="G638" s="110" t="str">
         <x:v>A/B｜正史直载或多源互证</x:v>
